--- a/diseases/d183/2000-2004.xlsx
+++ b/diseases/d183/2000-2004.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1498,6 +1523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1643,6 +1673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1788,6 +1823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2223,6 +2273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2368,6 +2423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2513,6 +2573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2948,6 +3023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3238,6 +3323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3383,6 +3473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3528,6 +3623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3818,6 +3923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4398,6 +4523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4543,6 +4673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4688,6 +4823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4833,6 +4973,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4978,6 +5123,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5123,6 +5273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5268,6 +5423,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5413,6 +5573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5558,6 +5723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5703,6 +5873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5848,6 +6023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5993,6 +6173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6138,6 +6323,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6283,6 +6473,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6428,6 +6623,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6573,6 +6773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6718,6 +6923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6863,6 +7073,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7008,6 +7223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7153,6 +7373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7298,6 +7523,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7443,6 +7673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7586,6 +7821,11 @@
       <c r="S49" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">

--- a/diseases/d183/2000-2004.xlsx
+++ b/diseases/d183/2000-2004.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,22 +780,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,11 +903,6 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -935,22 +915,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1068,11 +1038,6 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1085,22 +1050,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1218,11 +1173,6 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1235,22 +1185,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1368,11 +1308,6 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1385,22 +1320,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1466,17 +1391,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1515,126 +1440,34 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>sha256:64ea94f958e513b1b6a728d57e9aca4baf23baf4ad0cc42b4d51195193810e0b</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN7" t="b">
-        <v>0</v>
+          <t>unknown</t>
+        </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -1647,12 +1480,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1667,12 +1500,12 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1567,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2001-05-14</t>
+          <t>2001-05-21</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1748,11 +1581,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
@@ -1770,12 +1598,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1785,11 +1608,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1855,17 +1673,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1890,179 +1708,80 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2001-05-14</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>fleckfieber</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Fleckfieber</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN9" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2089,17 +1808,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2124,178 +1843,80 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2001-05-21</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>sha256:64ea94f958e513b1b6a728d57e9aca4baf23baf4ad0cc42b4d51195193810e0b</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN10" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2327,12 +1948,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2357,101 +1978,80 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2001-05-21</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2478,17 +2078,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2513,179 +2113,80 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2001-05-21</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2001-05</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>fleckfieber</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Fleckfieber</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN12" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2248,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2764,11 +2265,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2781,22 +2277,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2897,12 +2383,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2914,11 +2400,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2931,22 +2412,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3047,12 +2518,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -3064,11 +2535,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3081,22 +2547,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3197,12 +2653,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3214,11 +2670,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3231,22 +2682,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3347,12 +2788,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3364,11 +2805,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3381,22 +2817,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3497,12 +2923,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3514,11 +2940,6 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3531,22 +2952,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3647,12 +3058,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3664,11 +3075,6 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3681,22 +3087,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3797,12 +3193,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3814,11 +3210,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3831,22 +3222,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3947,12 +3328,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3964,11 +3345,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3981,22 +3357,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4097,12 +3463,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -4114,11 +3480,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4131,22 +3492,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4247,12 +3598,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4264,11 +3615,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4281,22 +3627,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4397,12 +3733,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4414,11 +3750,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4431,22 +3762,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4547,12 +3868,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4564,11 +3885,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4581,22 +3897,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4697,12 +4003,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4714,11 +4020,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4731,22 +4032,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4847,12 +4138,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4864,11 +4155,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4881,22 +4167,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4997,12 +4273,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -5014,11 +4290,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5031,22 +4302,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5147,12 +4408,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -5164,11 +4425,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5181,22 +4437,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5297,12 +4543,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -5314,11 +4560,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5331,22 +4572,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5447,12 +4678,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5464,11 +4695,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5481,22 +4707,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5597,12 +4813,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5614,11 +4830,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5631,22 +4842,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5747,12 +4948,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5764,11 +4965,6 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5781,22 +4977,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5867,12 +5053,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5897,95 +5083,86 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-06-23</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6047,12 +5224,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -6064,11 +5241,6 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6081,22 +5253,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6197,12 +5359,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -6214,11 +5376,6 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6231,22 +5388,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6347,12 +5494,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6364,11 +5511,6 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6381,22 +5523,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6462,17 +5594,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6497,178 +5629,80 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>__source_native__</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>national_ifsG_notification_registry</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>country:DE:national</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>sha256:64ea94f958e513b1b6a728d57e9aca4baf23baf4ad0cc42b4d51195193810e0b</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>DE_RKI_SURVSTAT_source_native</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN38" t="b">
-        <v>0</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>source_observations_only</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>no_eligible_public_projection</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>source_observations_only</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6700,12 +5734,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6730,101 +5764,80 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ39" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -6851,17 +5864,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6886,179 +5899,80 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>fleckfieber</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>SRC_DE_RKI_SURVSTAT</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>Fleckfieber</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>country:DE-HE:national</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>direct_only</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>source-current</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN40" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7120,12 +6034,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -7137,11 +6051,6 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7154,22 +6063,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7270,12 +6169,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -7287,11 +6186,6 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7304,22 +6198,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7420,12 +6304,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -7437,11 +6321,6 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7454,22 +6333,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7570,12 +6439,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7587,11 +6456,6 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7604,22 +6468,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7720,12 +6574,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7737,11 +6591,6 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7754,22 +6603,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7870,12 +6709,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7887,11 +6726,6 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7904,22 +6738,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -8020,12 +6844,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -8037,11 +6861,6 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8054,22 +6873,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -8170,12 +6979,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -8187,11 +6996,6 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8204,22 +7008,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8320,12 +7114,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-09</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -8337,11 +7131,6 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8354,22 +7143,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8470,12 +7249,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-10-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-10</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -8487,11 +7266,6 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8504,22 +7278,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8620,12 +7384,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-11-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-11</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8637,11 +7401,6 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8654,22 +7413,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8770,12 +7519,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-12-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-12</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8787,11 +7536,6 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8804,23 +7548,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
@@ -8857,906 +7591,6 @@
         </is>
       </c>
       <c r="BC52" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>epidemic-typhus-fever</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>流行性斑疹伤寒</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>2004-07-01</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2004-07</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP53" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV53" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA53" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB53" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC53" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>epidemic-typhus-fever</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>流行性斑疹伤寒</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>2004-08-01</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2004-08</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP54" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
-      <c r="AT54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV54" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA54" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB54" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC54" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>epidemic-typhus-fever</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>流行性斑疹伤寒</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>2004-09-01</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2004-09</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP55" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr"/>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV55" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA55" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB55" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC55" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>epidemic-typhus-fever</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>流行性斑疹伤寒</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>2004-10-01</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2004-10</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV56" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA56" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC56" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>epidemic-typhus-fever</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>流行性斑疹伤寒</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>2004-11-01</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2004-11</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr"/>
-      <c r="AT57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV57" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA57" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB57" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC57" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>epidemic-typhus-fever</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>public_projection</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>D183</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Epidemic typhus fever</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>流行性斑疹伤寒</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Bacterial</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>2004-12-01</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2004-12</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP58" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr"/>
-      <c r="AT58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
-      <c r="AV58" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>open_api_or_portal_download</t>
-        </is>
-      </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>kdca_open_api</t>
-        </is>
-      </c>
-      <c r="BA58" t="inlineStr">
-        <is>
-          <t>Korea KDCA EID</t>
-        </is>
-      </c>
-      <c r="BB58" t="inlineStr">
-        <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
-        </is>
-      </c>
-      <c r="BC58" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -9888,7 +7722,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -9908,7 +7742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -9918,7 +7752,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d183/2000-2004.xlsx
+++ b/diseases/d183/2000-2004.xlsx
@@ -1391,17 +1391,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1440,34 +1440,126 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>sha256:64ea94f958e513b1b6a728d57e9aca4baf23baf4ad0cc42b4d51195193810e0b</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>rki_survstat</t>
@@ -1480,12 +1572,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1500,12 +1592,12 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1659,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2001-05-21</t>
+          <t>2001-05-14</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1581,6 +1673,11 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
@@ -1598,7 +1695,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1608,6 +1710,11 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1673,17 +1780,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1708,80 +1815,179 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2001-06-01</t>
+          <t>2001-05-14</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2001-06</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>fleckfieber</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Fleckfieber</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:DE-HE:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1808,17 +2014,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1843,80 +2049,178 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2001-07-01</t>
+          <t>2001-05-21</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2001-07</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>sha256:64ea94f958e513b1b6a728d57e9aca4baf23baf4ad0cc42b4d51195193810e0b</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>0</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -1948,12 +2252,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1978,80 +2282,101 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2001-08-01</t>
+          <t>2001-05-21</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2001-08</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2403,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2113,80 +2438,179 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2001-09-01</t>
+          <t>2001-05-21</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2001-09</t>
+          <t>2001-05</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>fleckfieber</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Fleckfieber</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:DE-HE:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -2248,12 +2672,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2001-10-01</t>
+          <t>2001-06-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2001-10</t>
+          <t>2001-06</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2383,12 +2807,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2001-11-01</t>
+          <t>2001-07-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2001-11</t>
+          <t>2001-07</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2518,12 +2942,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2001-12-01</t>
+          <t>2001-08-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2001-12</t>
+          <t>2001-08</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2653,12 +3077,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2002-01-01</t>
+          <t>2001-09-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2002-01</t>
+          <t>2001-09</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2788,12 +3212,12 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2002-02-01</t>
+          <t>2001-10-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2002-02</t>
+          <t>2001-10</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2923,12 +3347,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2002-03-01</t>
+          <t>2001-11-01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2002-03</t>
+          <t>2001-11</t>
         </is>
       </c>
       <c r="N18" t="n">
@@ -3058,12 +3482,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2002-04-01</t>
+          <t>2001-12-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2002-04</t>
+          <t>2001-12</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3193,12 +3617,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2002-05-01</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2002-05</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3328,12 +3752,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2002-06-01</t>
+          <t>2002-02-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2002-06</t>
+          <t>2002-02</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3463,12 +3887,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2002-07-01</t>
+          <t>2002-03-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2002-07</t>
+          <t>2002-03</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3598,12 +4022,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2002-08-01</t>
+          <t>2002-04-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2002-08</t>
+          <t>2002-04</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -3733,12 +4157,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2002-09-01</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2002-09</t>
+          <t>2002-05</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -3868,12 +4292,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2002-10-01</t>
+          <t>2002-06-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2002-10</t>
+          <t>2002-06</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4003,12 +4427,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2002-11-01</t>
+          <t>2002-07-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2002-11</t>
+          <t>2002-07</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4138,12 +4562,12 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2002-12-01</t>
+          <t>2002-08-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2002-12</t>
+          <t>2002-08</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4273,12 +4697,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2003-01-01</t>
+          <t>2002-09-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2003-01</t>
+          <t>2002-09</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4408,12 +4832,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2002-10-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2002-10</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4543,12 +4967,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2002-11-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2002-11</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4678,12 +5102,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2002-12-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2002-12</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -4813,12 +5237,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -4948,12 +5372,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5053,12 +5477,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5083,33 +5507,31 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2003-06-23</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
@@ -5117,52 +5539,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
-        </is>
-      </c>
+      <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5224,12 +5642,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5359,12 +5777,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5494,12 +5912,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -5594,17 +6012,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5629,80 +6047,178 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-06-23</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SER_DE_RKI_SURVSTAT_SOURCE_NATIVE</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>__source_native__</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>national_ifsG_notification_registry</t>
+        </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>country:DE:national</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>sha256:64ea94f958e513b1b6a728d57e9aca4baf23baf4ad0cc42b4d51195193810e0b</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>DE_RKI_SURVSTAT_source_native</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Source-native RKI SurvStat category. The original pathogen/category is retained in dimensions and is not automatically rolled up.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN38" t="b">
+        <v>0</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -5734,12 +6250,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5764,80 +6280,101 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-06-23</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5864,17 +6401,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5899,80 +6436,179 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-06-23</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>fleckfieber</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SRC_DE_RKI_SURVSTAT</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Fleckfieber</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>country:DE-HE:national</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>direct_only</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>source-current</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN40" t="b">
+        <v>1</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>HOLD_DE_37b1903e58d82e9b48024879d35f</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6034,12 +6670,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6169,12 +6805,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6304,12 +6940,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6439,12 +7075,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -6574,12 +7210,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -6709,12 +7345,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -6844,12 +7480,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -6979,12 +7615,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7114,12 +7750,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7249,12 +7885,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7384,12 +8020,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -7519,12 +8155,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -7591,6 +8227,816 @@
         </is>
       </c>
       <c r="BC52" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2004-07-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2004-07</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2004-08-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2004-08</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>epidemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D183</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Epidemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>流行性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -7722,7 +9168,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -7742,7 +9188,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -7752,7 +9198,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d183/2000-2004.xlsx
+++ b/diseases/d183/2000-2004.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,12 +785,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -903,6 +918,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -915,12 +935,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1038,6 +1068,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1050,12 +1085,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1173,6 +1218,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1185,12 +1235,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1308,6 +1368,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1320,12 +1385,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -2689,6 +2764,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2701,12 +2781,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2824,6 +2914,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2836,12 +2931,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2959,6 +3064,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2971,12 +3081,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3094,6 +3214,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3106,12 +3231,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3229,6 +3364,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3241,12 +3381,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3364,6 +3514,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3376,12 +3531,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3499,6 +3664,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3511,12 +3681,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3634,6 +3814,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3646,12 +3831,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3769,6 +3964,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3781,12 +3981,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3904,6 +4114,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3916,12 +4131,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4039,6 +4264,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4051,12 +4281,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4174,6 +4414,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4186,12 +4431,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4309,6 +4564,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4321,12 +4581,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4444,6 +4714,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4456,12 +4731,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4579,6 +4864,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4591,12 +4881,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4714,6 +5014,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4726,12 +5031,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4849,6 +5164,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4861,12 +5181,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4984,6 +5314,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4996,12 +5331,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5119,6 +5464,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5131,12 +5481,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5254,6 +5614,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5266,12 +5631,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5389,6 +5764,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5401,12 +5781,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5524,6 +5914,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5536,12 +5931,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5659,6 +6064,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5671,12 +6081,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5794,6 +6214,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5806,12 +6231,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5929,6 +6364,11 @@
       <c r="R37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5941,12 +6381,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6687,6 +7137,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6699,12 +7154,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6822,6 +7287,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6834,12 +7304,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6957,6 +7437,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6969,12 +7454,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7092,6 +7587,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7104,12 +7604,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7227,6 +7737,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7239,12 +7754,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7362,6 +7887,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7374,12 +7904,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7497,6 +8037,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7509,12 +8054,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7632,6 +8187,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7644,12 +8204,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7767,6 +8337,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7779,12 +8354,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7902,6 +8487,11 @@
       <c r="R50" t="n">
         <v>0</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7914,12 +8504,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8037,6 +8637,11 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8049,12 +8654,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8172,6 +8787,11 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8184,12 +8804,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8307,6 +8937,11 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8319,12 +8954,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8442,6 +9087,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8454,12 +9104,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8577,6 +9237,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8589,12 +9254,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8712,6 +9387,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8724,12 +9404,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8847,6 +9537,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8859,12 +9554,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8982,6 +9687,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8994,12 +9704,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
